--- a/card_definitions.xlsx
+++ b/card_definitions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tuiko\remake_project\remake project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17254359-8CBF-470B-A20C-AC394381C72E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99465A69-CF9C-410F-90A6-EB525E706FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="Prices">Prices!$A:$B</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="78">
   <si>
     <t>이름</t>
   </si>
@@ -254,6 +254,38 @@
   </si>
   <si>
     <t>EnergyDrain</t>
+  </si>
+  <si>
+    <t>Sap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnergyHeal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnergyDrain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreatWall</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Defend</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DrainShield</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weak</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>neutralize</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -646,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -949,7 +981,7 @@
         <v>3</v>
       </c>
       <c r="H15">
-        <f t="shared" ref="H15:H36" si="1">IFERROR(VLOOKUP(B15,Prices,2,0)*ABS(C15),0)+IFERROR(VLOOKUP(D15,Prices,2,0)*ABS(E15),0)+IFERROR(VLOOKUP(F15,Prices,2,0)*ABS(G15),0)</f>
+        <f t="shared" ref="H15:H37" si="1">IFERROR(VLOOKUP(B15,Prices,2,0)*ABS(C15),0)+IFERROR(VLOOKUP(D15,Prices,2,0)*ABS(E15),0)+IFERROR(VLOOKUP(F15,Prices,2,0)*ABS(G15),0)</f>
         <v>3.5</v>
       </c>
       <c r="I15">
@@ -1228,9 +1260,30 @@
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
       <c r="H27">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12.4</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27">
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1384,15 +1437,24 @@
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34">
+        <v>30</v>
+      </c>
       <c r="H34">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I34">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J34">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1423,9 +1485,51 @@
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
       <c r="H36">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.2</v>
+      </c>
+      <c r="I36">
+        <v>3</v>
+      </c>
+      <c r="J36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37">
+        <v>5</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I37">
+        <v>2</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1472,7 +1576,7 @@
         <v>56</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
